--- a/output/roomself_excel/8763.xlsx
+++ b/output/roomself_excel/8763.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>84378</v>
+        <v>190930</v>
       </c>
       <c r="D2" t="n">
-        <v>2324</v>
+        <v>3724</v>
       </c>
       <c r="E2" t="n">
-        <v>320</v>
+        <v>626</v>
       </c>
       <c r="F2" t="n">
-        <v>316</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>237170</v>
+        <v>84378</v>
       </c>
       <c r="D3" t="n">
-        <v>4364</v>
+        <v>2324</v>
       </c>
       <c r="E3" t="n">
-        <v>848</v>
+        <v>320</v>
       </c>
       <c r="F3" t="n">
-        <v>625</v>
+        <v>316</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>41630</v>
+        <v>78792</v>
       </c>
       <c r="D4" t="n">
-        <v>1644</v>
+        <v>2248</v>
       </c>
       <c r="E4" t="n">
-        <v>259</v>
+        <v>320</v>
       </c>
       <c r="F4" t="n">
-        <v>207</v>
+        <v>294</v>
       </c>
     </row>
     <row r="5">
@@ -532,17 +532,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>24797</v>
+        <v>80500</v>
       </c>
       <c r="D5" t="n">
-        <v>1272</v>
+        <v>2288</v>
       </c>
       <c r="E5" t="n">
-        <v>137</v>
+        <v>322</v>
       </c>
       <c r="F5" t="n">
         <v>26</v>
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>78792</v>
+        <v>46240</v>
       </c>
       <c r="D6" t="n">
-        <v>2248</v>
+        <v>1796</v>
       </c>
       <c r="E6" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>294</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>80500</v>
+        <v>15385</v>
       </c>
       <c r="D7" t="n">
-        <v>2288</v>
+        <v>1064</v>
       </c>
       <c r="E7" t="n">
-        <v>544</v>
+        <v>207</v>
       </c>
       <c r="F7" t="n">
-        <v>214</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8">
@@ -602,16 +602,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>13213</v>
+        <v>41630</v>
       </c>
       <c r="D8" t="n">
-        <v>1016</v>
+        <v>1644</v>
       </c>
       <c r="E8" t="n">
-        <v>73</v>
+        <v>259</v>
       </c>
       <c r="F8" t="n">
-        <v>26</v>
+        <v>207</v>
       </c>
     </row>
     <row r="9">
@@ -624,13 +624,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10170</v>
+        <v>24797</v>
       </c>
       <c r="D9" t="n">
-        <v>812</v>
+        <v>1272</v>
       </c>
       <c r="E9" t="n">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="F9" t="n">
         <v>26</v>
@@ -646,13 +646,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>14670</v>
+        <v>13213</v>
       </c>
       <c r="D10" t="n">
-        <v>1012</v>
+        <v>1016</v>
       </c>
       <c r="E10" t="n">
-        <v>163</v>
+        <v>73</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
@@ -664,20 +664,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>15385</v>
+        <v>10170</v>
       </c>
       <c r="D11" t="n">
-        <v>1064</v>
+        <v>812</v>
       </c>
       <c r="E11" t="n">
-        <v>207</v>
+        <v>113</v>
       </c>
       <c r="F11" t="n">
-        <v>111</v>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>14670</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1012</v>
+      </c>
+      <c r="E12" t="n">
+        <v>163</v>
+      </c>
+      <c r="F12" t="n">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/8763.xlsx
+++ b/output/roomself_excel/8763.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,12 +495,20 @@
       <c r="D2" t="n">
         <v>3724</v>
       </c>
-      <c r="E2" t="n">
-        <v>626</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
+        <v>613</v>
+      </c>
+      <c r="G2" t="n">
         <v>29</v>
       </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,11 +525,27 @@
       <c r="D3" t="n">
         <v>2324</v>
       </c>
-      <c r="E3" t="n">
-        <v>320</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>316</v>
+        <v>294</v>
+      </c>
+      <c r="G3" t="n">
+        <v>29</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>287</v>
+      </c>
+      <c r="J3" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -519,11 +563,27 @@
       <c r="D4" t="n">
         <v>2248</v>
       </c>
-      <c r="E4" t="n">
-        <v>320</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F4" t="n">
+        <v>268</v>
+      </c>
+      <c r="G4" t="n">
+        <v>26</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>294</v>
+      </c>
+      <c r="J4" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="5">
@@ -541,12 +601,20 @@
       <c r="D5" t="n">
         <v>2288</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>322</v>
       </c>
-      <c r="F5" t="n">
-        <v>26</v>
-      </c>
+      <c r="G5" t="n">
+        <v>26</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +631,12 @@
       <c r="D6" t="n">
         <v>1796</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,11 +653,27 @@
       <c r="D7" t="n">
         <v>1064</v>
       </c>
-      <c r="E7" t="n">
-        <v>207</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>111</v>
+        <v>85</v>
+      </c>
+      <c r="G7" t="n">
+        <v>26</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>181</v>
+      </c>
+      <c r="J7" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="8">
@@ -607,11 +691,27 @@
       <c r="D8" t="n">
         <v>1644</v>
       </c>
-      <c r="E8" t="n">
-        <v>259</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>207</v>
+        <v>181</v>
+      </c>
+      <c r="G8" t="n">
+        <v>29</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>230</v>
+      </c>
+      <c r="J8" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="9">
@@ -629,12 +729,20 @@
       <c r="D9" t="n">
         <v>1272</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>137</v>
       </c>
-      <c r="F9" t="n">
-        <v>26</v>
-      </c>
+      <c r="G9" t="n">
+        <v>26</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +759,20 @@
       <c r="D10" t="n">
         <v>1016</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>73</v>
       </c>
-      <c r="F10" t="n">
-        <v>26</v>
-      </c>
+      <c r="G10" t="n">
+        <v>26</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +789,20 @@
       <c r="D11" t="n">
         <v>812</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>113</v>
       </c>
-      <c r="F11" t="n">
-        <v>26</v>
-      </c>
+      <c r="G11" t="n">
+        <v>26</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +819,20 @@
       <c r="D12" t="n">
         <v>1012</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>163</v>
       </c>
-      <c r="F12" t="n">
-        <v>26</v>
-      </c>
+      <c r="G12" t="n">
+        <v>26</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
